--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_teamExp.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_teamExp.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1282,7 +1282,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>13000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1293,7 +1293,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>16000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1304,7 +1304,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1">
-        <v>19000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1315,7 +1315,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>22000</v>
+        <v>34000</v>
       </c>
     </row>
   </sheetData>
